--- a/data/trans_camb/IP1019-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1019-Habitat-trans_camb.xlsx
@@ -631,27 +631,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 0,0</t>
+          <t>-2,6; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,0</t>
+          <t>-1,66; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,0</t>
+          <t>-0,5; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
